--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A0D7E6D-D82F-4E9A-9DEA-A9AE82D3B9FF}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AF0723C-012E-48CA-9FA7-07EF2C6AC0D5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,15 @@
   </si>
   <si>
     <t>AUGUST</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>spend mostof time in induction so it is motivational and knowledge based day. Learn most of the communities and other clubs at LPU.</t>
   </si>
 </sst>
 </file>
@@ -1030,27 +1039,51 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+    <row r="7" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B7" s="14">
+        <v>390</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>90</v>
+      </c>
+      <c r="E7" s="14">
+        <v>90</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>510</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AF0723C-012E-48CA-9FA7-07EF2C6AC0D5}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAD5F233-E97C-4AC4-99AB-63E79547DBAD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,7 +214,13 @@
     <t>High</t>
   </si>
   <si>
-    <t>spend mostof time in induction so it is motivational and knowledge based day. Learn most of the communities and other clubs at LPU.</t>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>spend most of time in induction so it is motivational and knowledge based day. Learn most of the communities and other clubs at LPU.</t>
+  </si>
+  <si>
+    <t>in the evening, apart from my college studies, I studied a software develpoment course.</t>
   </si>
 </sst>
 </file>
@@ -1082,30 +1088,54 @@
         <v>58</v>
       </c>
       <c r="N7" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14">
+        <v>150</v>
+      </c>
+      <c r="G8" s="14">
+        <v>3</v>
+      </c>
+      <c r="H8" s="14">
+        <v>120</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="1"/>
+        <v>540</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAD5F233-E97C-4AC4-99AB-63E79547DBAD}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86298FD9-FAA2-40E0-9AFE-0723CF0C0B89}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,15 @@
   </si>
   <si>
     <t>in the evening, apart from my college studies, I studied a software develpoment course.</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>today I learn git in advance</t>
+  </si>
+  <si>
+    <t>more focus on new skills</t>
   </si>
 </sst>
 </file>
@@ -1138,48 +1147,96 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>90</v>
+      </c>
+      <c r="F9" s="14">
+        <v>250</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5</v>
+      </c>
+      <c r="H9" s="14">
+        <v>90</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B10" s="14">
+        <v>420</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>240</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86298FD9-FAA2-40E0-9AFE-0723CF0C0B89}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFED940E-4D33-407E-9598-6E1C12E30A57}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>more focus on new skills</t>
+  </si>
+  <si>
+    <t>I felt little bit tired after studying 4 hours continuously.</t>
   </si>
 </sst>
 </file>
@@ -1238,27 +1241,51 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+    <row r="11" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>180</v>
+      </c>
+      <c r="E11" s="14">
+        <v>120</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFED940E-4D33-407E-9598-6E1C12E30A57}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D54D0D4-4373-4AB1-BE86-53E50B73F591}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>I felt little bit tired after studying 4 hours continuously.</t>
+  </si>
+  <si>
+    <t>getting busy all day is my favourite day.</t>
   </si>
 </sst>
 </file>
@@ -1287,27 +1290,51 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+    <row r="12" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D54D0D4-4373-4AB1-BE86-53E50B73F591}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF359DFC-6FB9-4A3A-A2BC-B180241635A6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,12 @@
   </si>
   <si>
     <t>getting busy all day is my favourite day.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>I felt low whole day because of cold and cough.</t>
   </si>
 </sst>
 </file>
@@ -1336,27 +1342,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+    <row r="13" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>120</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hi\OneDrive\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF359DFC-6FB9-4A3A-A2BC-B180241635A6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,15 @@
   </si>
   <si>
     <t>I felt low whole day because of cold and cough.</t>
+  </si>
+  <si>
+    <t>I felt tired after attended all 7  classes</t>
+  </si>
+  <si>
+    <t>I am not well today that's why energy level is low</t>
+  </si>
+  <si>
+    <t>today I feel energetic</t>
   </si>
 </sst>
 </file>
@@ -1388,71 +1397,143 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B14" s="14">
+        <v>360</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>90</v>
+      </c>
+      <c r="E15" s="14">
+        <v>120</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B16" s="14">
+        <v>360</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>200</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hi\OneDrive\Desktop\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C43B0E4-CA58-46FB-9FD2-864462CBF618}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>today I feel energetic</t>
+  </si>
+  <si>
+    <t>I felt energetic as I study in library the whole day</t>
   </si>
 </sst>
 </file>
@@ -1535,27 +1538,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+    <row r="17" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>300</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C43B0E4-CA58-46FB-9FD2-864462CBF618}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B41D935-F3E7-49B1-A587-F8BDF2307F6B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>I felt energetic as I study in library the whole day</t>
+  </si>
+  <si>
+    <t>I done extra credential courses.</t>
+  </si>
+  <si>
+    <t>energy level from the first lecture is very high.</t>
   </si>
 </sst>
 </file>
@@ -1585,48 +1591,96 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>180</v>
+      </c>
+      <c r="E18" s="14">
+        <v>180</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>90</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B19" s="14">
+        <v>360</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>90</v>
+      </c>
+      <c r="F19" s="14">
+        <v>250</v>
+      </c>
+      <c r="G19" s="14">
+        <v>5</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B41D935-F3E7-49B1-A587-F8BDF2307F6B}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BCB09B4-0178-428D-9085-EF2046925EBB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,12 @@
   </si>
   <si>
     <t>energy level from the first lecture is very high.</t>
+  </si>
+  <si>
+    <t>I practice python programming.</t>
+  </si>
+  <si>
+    <t>today I feel hectic so I don't study</t>
   </si>
 </sst>
 </file>
@@ -1682,49 +1688,97 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+    <row r="20" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B20" s="14">
+        <v>360</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>90</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B21" s="14">
+        <v>360</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BCB09B4-0178-428D-9085-EF2046925EBB}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52E0DEAD-EB95-4993-AD22-FF279780F217}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1781,26 +1781,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B22" s="14">
+        <v>360</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>180</v>
+      </c>
+      <c r="E22" s="14">
+        <v>90</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52E0DEAD-EB95-4993-AD22-FF279780F217}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A4BBB96-97AB-4306-8C52-BC93B4C8E876}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,21 @@
   </si>
   <si>
     <t>today I feel hectic so I don't study</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>I attend lecture and celeb rakhi in campus.</t>
+  </si>
+  <si>
+    <t>I go to my home to meet family members.</t>
+  </si>
+  <si>
+    <t>spend time with my family.</t>
+  </si>
+  <si>
+    <t>again attend classes and in evening I felt so hungry.</t>
   </si>
 </sst>
 </file>
@@ -1826,93 +1841,189 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+    <row r="23" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B23" s="14">
+        <v>360</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>180</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
+      <c r="F23" s="14">
+        <v>150</v>
+      </c>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>90</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>180</v>
+      </c>
+      <c r="E25" s="14">
+        <v>120</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>120</v>
+      </c>
+      <c r="F26" s="14">
+        <v>250</v>
+      </c>
+      <c r="G26" s="14">
+        <v>5</v>
+      </c>
+      <c r="H26" s="14">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A4BBB96-97AB-4306-8C52-BC93B4C8E876}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B3052C2-0E8C-4A98-A3C3-4FD9ACC7ACAE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -205,9 +205,6 @@
     <t>MCA/D1P2636</t>
   </si>
   <si>
-    <t>AUGUST</t>
-  </si>
-  <si>
     <t>Excellent</t>
   </si>
   <si>
@@ -281,6 +278,12 @@
   </si>
   <si>
     <t>again attend classes and in evening I felt so hungry.</t>
+  </si>
+  <si>
+    <t>SEPTEMBER</t>
+  </si>
+  <si>
+    <t>full energetic to learn new things</t>
   </si>
 </sst>
 </file>
@@ -993,7 +996,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1139,16 +1142,16 @@
         <v>360</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -1188,13 +1191,13 @@
         <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -1231,16 +1234,16 @@
         <v>470</v>
       </c>
       <c r="K9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L9" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N9" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -1280,13 +1283,13 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -1332,7 +1335,7 @@
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -1369,16 +1372,16 @@
         <v>500</v>
       </c>
       <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L12" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N12" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -1415,16 +1418,16 @@
         <v>490</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="17" t="s">
         <v>67</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -1470,7 +1473,7 @@
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -1507,16 +1510,16 @@
         <v>610</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
@@ -1553,16 +1556,16 @@
         <v>640</v>
       </c>
       <c r="K16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L16" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N16" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -1602,13 +1605,13 @@
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
@@ -1645,16 +1648,16 @@
         <v>570</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -1691,16 +1694,16 @@
         <v>620</v>
       </c>
       <c r="K19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M19" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L19" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N19" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -1737,16 +1740,16 @@
         <v>640</v>
       </c>
       <c r="K20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L20" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N20" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
@@ -1792,7 +1795,7 @@
         <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -1829,16 +1832,16 @@
         <v>560</v>
       </c>
       <c r="K22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L22" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N22" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -1875,7 +1878,7 @@
         <v>630</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>50</v>
@@ -1884,7 +1887,7 @@
         <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -1921,16 +1924,16 @@
         <v>690</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
@@ -1967,16 +1970,16 @@
         <v>720</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2013,39 +2016,63 @@
         <v>590</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>180</v>
+      </c>
+      <c r="E27" s="14">
+        <v>120</v>
+      </c>
+      <c r="F27" s="14">
+        <v>350</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>30</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B3052C2-0E8C-4A98-A3C3-4FD9ACC7ACAE}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{160E75E5-4A55-485A-9769-08FACF01ABDC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>full energetic to learn new things</t>
+  </si>
+  <si>
+    <t>today  I learn javascript as extra skill</t>
   </si>
 </sst>
 </file>
@@ -2074,27 +2077,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+    <row r="28" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B28" s="14">
+        <v>360</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>170</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>250</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>
